--- a/public/Completion_Importing_Template.xlsx
+++ b/public/Completion_Importing_Template.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jaica\OneDrive\Desktop\PS\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jaica\OneDrive\Desktop\PS\public\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F8A4DBB5-773F-4F6E-904D-8A53F1E81FD4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{35A35366-9525-4F87-9D0B-CCD1A77AC037}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21075" windowHeight="13695" xr2:uid="{28108F55-8346-401A-B717-A4C0635FECEB}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
   <si>
     <t>Date From</t>
   </si>
@@ -54,16 +54,7 @@
     <t>Destination</t>
   </si>
   <si>
-    <t>Butuan City</t>
-  </si>
-  <si>
-    <t>James E. Rosales</t>
-  </si>
-  <si>
     <t>Unit</t>
-  </si>
-  <si>
-    <t>DRRM</t>
   </si>
   <si>
     <t>Time Start</t>
@@ -153,14 +144,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="15" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -168,9 +156,6 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="18" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -485,22 +470,22 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0CAD3974-0F7B-413B-9962-A1A83CE8234D}">
-  <dimension ref="A1:J2"/>
+  <dimension ref="A1:J1"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="9.06640625" style="7"/>
+    <col min="1" max="1" width="9.06640625" style="6"/>
     <col min="2" max="2" width="38.73046875" style="1" customWidth="1"/>
     <col min="3" max="3" width="21.46484375" style="1" customWidth="1"/>
-    <col min="4" max="4" width="11.3984375" style="5" customWidth="1"/>
-    <col min="5" max="7" width="10.86328125" style="5" customWidth="1"/>
+    <col min="4" max="4" width="11.3984375" style="4" customWidth="1"/>
+    <col min="5" max="7" width="10.86328125" style="4" customWidth="1"/>
     <col min="8" max="8" width="23.06640625" style="1" customWidth="1"/>
     <col min="9" max="9" width="22.33203125" style="1" customWidth="1"/>
     <col min="10" max="10" width="21.59765625" style="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A1" s="6" t="s">
-        <v>7</v>
+      <c r="A1" s="5" t="s">
+        <v>5</v>
       </c>
       <c r="B1" s="2" t="s">
         <v>3</v>
@@ -515,48 +500,19 @@
         <v>1</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="H1" s="2" t="s">
         <v>2</v>
       </c>
       <c r="I1" s="2" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="J1" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A2" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D2" s="4">
-        <v>46294</v>
-      </c>
-      <c r="E2" s="4">
-        <v>46296</v>
-      </c>
-      <c r="F2" s="8">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="G2" s="8">
-        <v>0.70833333333333337</v>
-      </c>
-      <c r="H2" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="I2" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
   </sheetData>

--- a/public/Completion_Importing_Template.xlsx
+++ b/public/Completion_Importing_Template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jaica\OneDrive\Desktop\PS\public\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{35A35366-9525-4F87-9D0B-CCD1A77AC037}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FD76EEA8-BACD-4548-A6F8-23506C560928}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21075" windowHeight="13695" xr2:uid="{28108F55-8346-401A-B717-A4C0635FECEB}"/>
   </bookViews>
@@ -103,7 +103,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -113,6 +113,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF002060"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-0.499984740745262"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -144,18 +150,23 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -473,45 +484,46 @@
   <dimension ref="A1:J1"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="9.06640625" style="6"/>
-    <col min="2" max="2" width="38.73046875" style="1" customWidth="1"/>
-    <col min="3" max="3" width="21.46484375" style="1" customWidth="1"/>
-    <col min="4" max="4" width="11.3984375" style="4" customWidth="1"/>
-    <col min="5" max="7" width="10.86328125" style="4" customWidth="1"/>
-    <col min="8" max="8" width="23.06640625" style="1" customWidth="1"/>
-    <col min="9" max="9" width="22.33203125" style="1" customWidth="1"/>
-    <col min="10" max="10" width="21.59765625" style="1" customWidth="1"/>
+    <col min="1" max="1" width="9.06640625" style="4"/>
+    <col min="2" max="2" width="38.73046875" style="5" customWidth="1"/>
+    <col min="3" max="3" width="21.46484375" style="5" customWidth="1"/>
+    <col min="4" max="4" width="11.3984375" style="5" customWidth="1"/>
+    <col min="5" max="7" width="10.86328125" style="5" customWidth="1"/>
+    <col min="8" max="8" width="23.06640625" style="5" customWidth="1"/>
+    <col min="9" max="9" width="22.33203125" style="5" customWidth="1"/>
+    <col min="10" max="10" width="21.59765625" style="5" customWidth="1"/>
+    <col min="11" max="16384" width="9.06640625" style="6"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A1" s="5" t="s">
+    <row r="1" spans="1:10" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="A1" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="D1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="E1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="F1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="G1" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="H1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="I1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="2" t="s">
+      <c r="J1" s="7" t="s">
         <v>9</v>
       </c>
     </row>

--- a/public/Completion_Importing_Template.xlsx
+++ b/public/Completion_Importing_Template.xlsx
@@ -8,12 +8,12 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jaica\OneDrive\Desktop\PS\public\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FD76EEA8-BACD-4548-A6F8-23506C560928}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{69EAB640-FE59-45EE-95E6-B60F62BBB596}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="21075" windowHeight="13695" xr2:uid="{28108F55-8346-401A-B717-A4C0635FECEB}"/>
+    <workbookView xWindow="1837" yWindow="1837" windowWidth="15661" windowHeight="9848" xr2:uid="{28108F55-8346-401A-B717-A4C0635FECEB}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Completion" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>

--- a/public/Completion_Importing_Template.xlsx
+++ b/public/Completion_Importing_Template.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jaica\OneDrive\Desktop\PS\public\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{69EAB640-FE59-45EE-95E6-B60F62BBB596}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ABFB81C9-9F98-40EB-92C7-4D90CD913473}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1837" yWindow="1837" windowWidth="15661" windowHeight="9848" xr2:uid="{28108F55-8346-401A-B717-A4C0635FECEB}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="21075" windowHeight="13695" xr2:uid="{28108F55-8346-401A-B717-A4C0635FECEB}"/>
   </bookViews>
   <sheets>
     <sheet name="Completion" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
   <si>
     <t>Date From</t>
   </si>
@@ -64,9 +64,6 @@
   </si>
   <si>
     <t>Distribution Place</t>
-  </si>
-  <si>
-    <t>Distribution Date</t>
   </si>
 </sst>
 </file>
@@ -103,7 +100,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -113,12 +110,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF002060"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="0" tint="-0.499984740745262"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -150,7 +141,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -166,7 +157,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -481,7 +471,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0CAD3974-0F7B-413B-9962-A1A83CE8234D}">
-  <dimension ref="A1:J1"/>
+  <dimension ref="A1:I1"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="9.06640625" style="4"/>
@@ -491,11 +481,10 @@
     <col min="5" max="7" width="10.86328125" style="5" customWidth="1"/>
     <col min="8" max="8" width="23.06640625" style="5" customWidth="1"/>
     <col min="9" max="9" width="22.33203125" style="5" customWidth="1"/>
-    <col min="10" max="10" width="21.59765625" style="5" customWidth="1"/>
-    <col min="11" max="16384" width="9.06640625" style="6"/>
+    <col min="10" max="16384" width="9.06640625" style="6"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:9" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A1" s="3" t="s">
         <v>5</v>
       </c>
@@ -522,9 +511,6 @@
       </c>
       <c r="I1" s="1" t="s">
         <v>8</v>
-      </c>
-      <c r="J1" s="7" t="s">
-        <v>9</v>
       </c>
     </row>
   </sheetData>

--- a/public/Completion_Importing_Template.xlsx
+++ b/public/Completion_Importing_Template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jaica\OneDrive\Desktop\PS\public\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ABFB81C9-9F98-40EB-92C7-4D90CD913473}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{20C4217C-1391-4032-A849-7A43379A9A02}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21075" windowHeight="13695" xr2:uid="{28108F55-8346-401A-B717-A4C0635FECEB}"/>
   </bookViews>
@@ -514,6 +514,19 @@
       </c>
     </row>
   </sheetData>
+  <dataValidations count="3">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A2:A1048576" xr:uid="{66AF9D4B-091B-4C6E-90B0-0478D1C954FE}">
+      <formula1>"AGRISTAT, AMIA, DRRM"</formula1>
+    </dataValidation>
+    <dataValidation type="date" allowBlank="1" showInputMessage="1" showErrorMessage="1" error="The inputted date is out of the coverage." sqref="D2:D1048576 E2:E1048576" xr:uid="{36DC3C1F-51F0-41C5-97FB-4DB4F84A23DB}">
+      <formula1>46023</formula1>
+      <formula2>46752</formula2>
+    </dataValidation>
+    <dataValidation type="time" allowBlank="1" showInputMessage="1" showErrorMessage="1" error="The inputted time is out of the coverage." sqref="F2:F1048576 G2:G1048576" xr:uid="{7AC60022-AED5-49F6-A848-38E91A54CFC2}">
+      <formula1>0.208333333333333</formula1>
+      <formula2>0.833333333333333</formula2>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/public/Completion_Importing_Template.xlsx
+++ b/public/Completion_Importing_Template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jaica\OneDrive\Desktop\PS\public\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{20C4217C-1391-4032-A849-7A43379A9A02}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A30DECE9-4EEC-4376-8C2D-DECC413DAD27}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21075" windowHeight="13695" xr2:uid="{28108F55-8346-401A-B717-A4C0635FECEB}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
   <si>
     <t>Date From</t>
   </si>
@@ -55,12 +55,6 @@
   </si>
   <si>
     <t>Unit</t>
-  </si>
-  <si>
-    <t>Time Start</t>
-  </si>
-  <si>
-    <t>Time End</t>
   </si>
   <si>
     <t>Distribution Place</t>
@@ -471,20 +465,20 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0CAD3974-0F7B-413B-9962-A1A83CE8234D}">
-  <dimension ref="A1:I1"/>
+  <dimension ref="A1:G1"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="9.06640625" style="4"/>
     <col min="2" max="2" width="38.73046875" style="5" customWidth="1"/>
     <col min="3" max="3" width="21.46484375" style="5" customWidth="1"/>
     <col min="4" max="4" width="11.3984375" style="5" customWidth="1"/>
-    <col min="5" max="7" width="10.86328125" style="5" customWidth="1"/>
-    <col min="8" max="8" width="23.06640625" style="5" customWidth="1"/>
-    <col min="9" max="9" width="22.33203125" style="5" customWidth="1"/>
-    <col min="10" max="16384" width="9.06640625" style="6"/>
+    <col min="5" max="5" width="10.86328125" style="5" customWidth="1"/>
+    <col min="6" max="6" width="23.06640625" style="5" customWidth="1"/>
+    <col min="7" max="7" width="22.33203125" style="5" customWidth="1"/>
+    <col min="8" max="16384" width="9.06640625" style="6"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:7" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A1" s="3" t="s">
         <v>5</v>
       </c>
@@ -500,21 +494,15 @@
       <c r="E1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="F1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="G1" s="1" t="s">
         <v>6</v>
-      </c>
-      <c r="G1" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>8</v>
       </c>
     </row>
   </sheetData>
-  <dataValidations count="3">
+  <dataValidations count="2">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A2:A1048576" xr:uid="{66AF9D4B-091B-4C6E-90B0-0478D1C954FE}">
       <formula1>"AGRISTAT, AMIA, DRRM"</formula1>
     </dataValidation>
@@ -522,10 +510,6 @@
       <formula1>46023</formula1>
       <formula2>46752</formula2>
     </dataValidation>
-    <dataValidation type="time" allowBlank="1" showInputMessage="1" showErrorMessage="1" error="The inputted time is out of the coverage." sqref="F2:F1048576 G2:G1048576" xr:uid="{7AC60022-AED5-49F6-A848-38E91A54CFC2}">
-      <formula1>0.208333333333333</formula1>
-      <formula2>0.833333333333333</formula2>
-    </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/public/Completion_Importing_Template.xlsx
+++ b/public/Completion_Importing_Template.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jaica\OneDrive\Desktop\PS\public\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jaica\OneDrive\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A30DECE9-4EEC-4376-8C2D-DECC413DAD27}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D517B4A9-9CA2-4398-8EBD-5F5B1FD7098B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21075" windowHeight="13695" xr2:uid="{28108F55-8346-401A-B717-A4C0635FECEB}"/>
   </bookViews>
@@ -54,10 +54,10 @@
     <t>Destination</t>
   </si>
   <si>
-    <t>Unit</t>
-  </si>
-  <si>
     <t>Distribution Place</t>
+  </si>
+  <si>
+    <t>Assignment</t>
   </si>
 </sst>
 </file>
@@ -468,7 +468,7 @@
   <dimension ref="A1:G1"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="9.06640625" style="4"/>
+    <col min="1" max="1" width="12.19921875" style="4" customWidth="1"/>
     <col min="2" max="2" width="38.73046875" style="5" customWidth="1"/>
     <col min="3" max="3" width="21.46484375" style="5" customWidth="1"/>
     <col min="4" max="4" width="11.3984375" style="5" customWidth="1"/>
@@ -480,7 +480,7 @@
   <sheetData>
     <row r="1" spans="1:7" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A1" s="3" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>3</v>
@@ -498,7 +498,7 @@
         <v>2</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>

--- a/public/Completion_Importing_Template.xlsx
+++ b/public/Completion_Importing_Template.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jaica\OneDrive\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jaica\OneDrive\Desktop\PS\public\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D517B4A9-9CA2-4398-8EBD-5F5B1FD7098B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E98365E-3FBA-4F88-8C91-119B5901A75B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21075" windowHeight="13695" xr2:uid="{28108F55-8346-401A-B717-A4C0635FECEB}"/>
   </bookViews>
@@ -57,7 +57,7 @@
     <t>Distribution Place</t>
   </si>
   <si>
-    <t>Assignment</t>
+    <t>Certificate Template From</t>
   </si>
 </sst>
 </file>
@@ -94,7 +94,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -104,6 +104,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF002060"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="-0.249977111117893"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -135,13 +141,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -150,6 +154,15 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -468,30 +481,29 @@
   <dimension ref="A1:G1"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="12.19921875" style="4" customWidth="1"/>
-    <col min="2" max="2" width="38.73046875" style="5" customWidth="1"/>
-    <col min="3" max="3" width="21.46484375" style="5" customWidth="1"/>
-    <col min="4" max="4" width="11.3984375" style="5" customWidth="1"/>
-    <col min="5" max="5" width="10.86328125" style="5" customWidth="1"/>
-    <col min="6" max="6" width="23.06640625" style="5" customWidth="1"/>
-    <col min="7" max="7" width="22.33203125" style="5" customWidth="1"/>
-    <col min="8" max="16384" width="9.06640625" style="6"/>
+    <col min="1" max="1" width="27.6640625" style="2" customWidth="1"/>
+    <col min="2" max="3" width="35.59765625" style="3" customWidth="1"/>
+    <col min="4" max="4" width="11.3984375" style="3" customWidth="1"/>
+    <col min="5" max="5" width="10.86328125" style="3" customWidth="1"/>
+    <col min="6" max="6" width="23.06640625" style="3" customWidth="1"/>
+    <col min="7" max="7" width="22.33203125" style="3" customWidth="1"/>
+    <col min="8" max="16384" width="9.06640625" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" customFormat="1" x14ac:dyDescent="0.45">
-      <c r="A1" s="3" t="s">
+    <row r="1" spans="1:7" s="6" customFormat="1" ht="35" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A1" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="1" t="s">
         <v>1</v>
       </c>
       <c r="F1" s="1" t="s">

--- a/public/Completion_Importing_Template.xlsx
+++ b/public/Completion_Importing_Template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jaica\OneDrive\Desktop\PS\public\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E98365E-3FBA-4F88-8C91-119B5901A75B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{524A0DCB-B225-4632-B7AE-E6482C02BCFC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21075" windowHeight="13695" xr2:uid="{28108F55-8346-401A-B717-A4C0635FECEB}"/>
   </bookViews>
@@ -94,7 +94,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -110,6 +110,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="4" tint="-0.249977111117893"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="2" tint="-0.749992370372631"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -141,17 +147,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -162,6 +162,15 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -481,23 +490,23 @@
   <dimension ref="A1:G1"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="27.6640625" style="2" customWidth="1"/>
-    <col min="2" max="3" width="35.59765625" style="3" customWidth="1"/>
-    <col min="4" max="4" width="11.3984375" style="3" customWidth="1"/>
-    <col min="5" max="5" width="10.86328125" style="3" customWidth="1"/>
-    <col min="6" max="6" width="23.06640625" style="3" customWidth="1"/>
-    <col min="7" max="7" width="22.33203125" style="3" customWidth="1"/>
-    <col min="8" max="16384" width="9.06640625" style="4"/>
+    <col min="1" max="1" width="27.6640625" style="6" customWidth="1"/>
+    <col min="2" max="3" width="35.59765625" style="7" customWidth="1"/>
+    <col min="4" max="4" width="11.3984375" style="7" customWidth="1"/>
+    <col min="5" max="5" width="10.86328125" style="7" customWidth="1"/>
+    <col min="6" max="6" width="23.06640625" style="7" customWidth="1"/>
+    <col min="7" max="7" width="22.33203125" style="7" customWidth="1"/>
+    <col min="8" max="16384" width="9.06640625" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" s="6" customFormat="1" ht="35" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A1" s="5" t="s">
+    <row r="1" spans="1:7" s="4" customFormat="1" ht="35" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A1" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="B1" s="7" t="s">
+      <c r="B1" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="C1" s="7" t="s">
+      <c r="C1" s="5" t="s">
         <v>4</v>
       </c>
       <c r="D1" s="1" t="s">
@@ -509,7 +518,7 @@
       <c r="F1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" s="8" t="s">
         <v>5</v>
       </c>
     </row>
